--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92563590306</v>
+        <v>46157.93080529016</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93080529016</v>
+        <v>46157.9315969646</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9315969646</v>
+        <v>46157.93395356424</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93395356424</v>
+        <v>46157.93712211668</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93712211668</v>
+        <v>46158.28212138139</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28212138139</v>
+        <v>46158.29673190314</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29673190314</v>
+        <v>46158.29808615287</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808615287</v>
+        <v>46158.33382936544</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33382936544</v>
+        <v>46158.36850756065</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36850756065</v>
+        <v>46158.37283093228</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
